--- a/SGC-CKN/Excel/fca79dba-739e-4a79-90bf-f16b01106569_Hạng_mục_Lô_CT-02_P2-12_D800_10-04-2026.xlsx
+++ b/SGC-CKN/Excel/fca79dba-739e-4a79-90bf-f16b01106569_Hạng_mục_Lô_CT-02_P2-12_D800_10-04-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P2-12</t>
+    <t>P2-17</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
